--- a/artfynd/A 65899-2021 artfynd.xlsx
+++ b/artfynd/A 65899-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 65899-2021 artfynd.xlsx
+++ b/artfynd/A 65899-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89603252</v>
+        <v>89603296</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>426224.7833284009</v>
+        <v>426046</v>
       </c>
       <c r="R2" t="n">
-        <v>6938047.898748354</v>
+        <v>6938180</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2020-10-14</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89603258</v>
+        <v>89603300</v>
       </c>
       <c r="B3" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>426163.8316186133</v>
+        <v>426059</v>
       </c>
       <c r="R3" t="n">
-        <v>6938111.061416408</v>
+        <v>6938152</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,19 +844,9 @@
           <t>2020-10-14</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>89603255</v>
+        <v>89603241</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>426179.805501059</v>
+        <v>426225</v>
       </c>
       <c r="R4" t="n">
-        <v>6938060.891709763</v>
+        <v>6938074</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,19 +945,9 @@
           <t>2020-10-14</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>89603286</v>
+        <v>89603248</v>
       </c>
       <c r="B5" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>426043.9017704432</v>
+        <v>426184</v>
       </c>
       <c r="R5" t="n">
-        <v>6938159.85655963</v>
+        <v>6938064</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,19 +1046,9 @@
           <t>2020-10-14</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,15 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>89603297</v>
+        <v>89603258</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1155,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>426184.9250575242</v>
+        <v>426164</v>
       </c>
       <c r="R6" t="n">
-        <v>6938041.866648851</v>
+        <v>6938111</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,19 +1147,9 @@
           <t>2020-10-14</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,15 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>89603277</v>
+        <v>89603265</v>
       </c>
       <c r="B7" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1271,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1295,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>426167.781405851</v>
+        <v>426074</v>
       </c>
       <c r="R7" t="n">
-        <v>6938080.992819151</v>
+        <v>6938171</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1328,19 +1248,9 @@
           <t>2020-10-14</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,15 +1281,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>89603282</v>
+        <v>89603294</v>
       </c>
       <c r="B8" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,21 +1292,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1411,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>426078.8141891417</v>
+        <v>426075</v>
       </c>
       <c r="R8" t="n">
-        <v>6938171.992915642</v>
+        <v>6938141</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1444,19 +1349,9 @@
           <t>2020-10-14</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,15 +1382,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>89603253</v>
+        <v>89603302</v>
       </c>
       <c r="B9" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1503,21 +1393,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1527,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>426094.2020701746</v>
+        <v>426217</v>
       </c>
       <c r="R9" t="n">
-        <v>6938137.057522058</v>
+        <v>6938041</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1560,19 +1450,9 @@
           <t>2020-10-14</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1603,37 +1483,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>89603302</v>
+        <v>89603243</v>
       </c>
       <c r="B10" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1643,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>426216.7809814057</v>
+        <v>426088</v>
       </c>
       <c r="R10" t="n">
-        <v>6938041.157995667</v>
+        <v>6938139</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1676,19 +1551,9 @@
           <t>2020-10-14</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1719,37 +1584,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>89603241</v>
+        <v>89603252</v>
       </c>
       <c r="B11" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1759,10 +1619,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>426224.9060348336</v>
+        <v>426225</v>
       </c>
       <c r="R11" t="n">
-        <v>6938074.187029637</v>
+        <v>6938048</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1792,19 +1652,9 @@
           <t>2020-10-14</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1835,37 +1685,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>89603294</v>
+        <v>89603255</v>
       </c>
       <c r="B12" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1875,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>426074.8942495373</v>
+        <v>426180</v>
       </c>
       <c r="R12" t="n">
-        <v>6938141.177616153</v>
+        <v>6938061</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1908,19 +1753,9 @@
           <t>2020-10-14</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1951,37 +1786,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>89603291</v>
+        <v>89603275</v>
       </c>
       <c r="B13" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1991,10 +1821,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>426158.9481149881</v>
+        <v>426199</v>
       </c>
       <c r="R13" t="n">
-        <v>6938099.177870019</v>
+        <v>6938068</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2024,19 +1854,9 @@
           <t>2020-10-14</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2067,37 +1887,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>89603265</v>
+        <v>89603277</v>
       </c>
       <c r="B14" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2107,10 +1922,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>426074.177022451</v>
+        <v>426168</v>
       </c>
       <c r="R14" t="n">
-        <v>6938171.173787966</v>
+        <v>6938081</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2140,19 +1955,9 @@
           <t>2020-10-14</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2183,37 +1988,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>89603248</v>
+        <v>89603282</v>
       </c>
       <c r="B15" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2223,10 +2023,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>426184.0324036632</v>
+        <v>426079</v>
       </c>
       <c r="R15" t="n">
-        <v>6938064.026376298</v>
+        <v>6938172</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2256,19 +2056,9 @@
           <t>2020-10-14</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2299,19 +2089,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>89603243</v>
+        <v>89603297</v>
       </c>
       <c r="B16" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2339,10 +2124,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>426087.7798202552</v>
+        <v>426185</v>
       </c>
       <c r="R16" t="n">
-        <v>6938139.045550878</v>
+        <v>6938042</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2372,19 +2157,9 @@
           <t>2020-10-14</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2415,15 +2190,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>89603296</v>
+        <v>89603245</v>
       </c>
       <c r="B17" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2431,21 +2201,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2455,10 +2225,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>426046.2006263736</v>
+        <v>426207</v>
       </c>
       <c r="R17" t="n">
-        <v>6938180.099516377</v>
+        <v>6938040</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2488,19 +2258,9 @@
           <t>2020-10-14</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2524,354 +2284,6 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>89603300</v>
-      </c>
-      <c r="B18" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>1108</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Harticka</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Stornäshållan, Hjd</t>
-        </is>
-      </c>
-      <c r="Q18" t="n">
-        <v>426058.9722662059</v>
-      </c>
-      <c r="R18" t="n">
-        <v>6938152.1408727</v>
-      </c>
-      <c r="S18" t="n">
-        <v>10</v>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Hede</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>89603275</v>
-      </c>
-      <c r="B19" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Stornäshållan, Hjd</t>
-        </is>
-      </c>
-      <c r="Q19" t="n">
-        <v>426198.8983698452</v>
-      </c>
-      <c r="R19" t="n">
-        <v>6938067.846837376</v>
-      </c>
-      <c r="S19" t="n">
-        <v>10</v>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Hede</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="inlineStr"/>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>89603245</v>
-      </c>
-      <c r="B20" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>6453</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Vedskivlav</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Hertelidea botryosa</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Stornäshållan, Hjd</t>
-        </is>
-      </c>
-      <c r="Q20" t="n">
-        <v>426207.0549352996</v>
-      </c>
-      <c r="R20" t="n">
-        <v>6938039.990578445</v>
-      </c>
-      <c r="S20" t="n">
-        <v>10</v>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>Hede</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>2020-10-14</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="inlineStr"/>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
         <is>
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>

--- a/artfynd/A 65899-2021 artfynd.xlsx
+++ b/artfynd/A 65899-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603296</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603300</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603241</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603248</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603258</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603265</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603294</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603302</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603243</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603252</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1783,6 +1838,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603255</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1884,6 +1944,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603275</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1985,6 +2050,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603277</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2086,6 +2156,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603282</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2187,6 +2262,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603297</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2288,8 +2368,31 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603245</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>